--- a/vragen/1000+ vragen netjes gecategoriseerd.xlsx
+++ b/vragen/1000+ vragen netjes gecategoriseerd.xlsx
@@ -4924,11 +4924,11 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Wat is het totale aantal pixels op een Full HD (1080p) beeldscherm in duizendtallen?</t>
+          <t>Hoeveel duizend beeldpunten telt een Full HD-scherm?</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Wat is de gemiddelde afstand van de Aarde tot de Zon in miljoenen kilometers?</t>
+          <t>Hoeveel miljoen kilometer is de gemiddelde afstand van de aarde tot de zon?</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Wat is de oppervlakte van het land Australië in duizend vierkante kilometer?</t>
+          <t>Hoeveel duizend vierkante kilometer groot is Australië?</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Wat is het gewicht van het zwaarste dier ooit op aarde (de Blauwe Vinvis) in duizend kilogram (ton)?</t>
+          <t>Hoeveel ton weegt een volwassen blauwe vinvis?</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -13492,11 +13492,11 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Hoeveel delen CO₂ per miljoen delen lucht noemt NASA momenteel als afgeronde waarde?</t>
+          <t>Hoeveel delen CO₂ per miljoen delen lucht meet NASA nu?</t>
         </is>
       </c>
       <c r="C623" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer hoog is de grens van de ruimte, de Karmanlijn, afgerond?</t>
+          <t>Hoeveel kilometer boven de aarde ligt de Kármánlijn, de grens van de ruimte?</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Hoeveel meter is de Challengerdiepte in de Marianentrog afgerond?</t>
+          <t>Hoeveel meter diep is de Challengerdiepte in de Marianentrog?</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -20149,11 +20149,11 @@
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>Hoeveel inwoners heeft Amsterdam ongeveer in duizendtallen (2024)?</t>
+          <t>Hoeveel duizend inwoners heeft Amsterdam?</t>
         </is>
       </c>
       <c r="C984" t="n">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="D984" t="inlineStr"/>
       <c r="E984" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Hoeveel km lang is de Hanzelijn spoorlijn Lelystad-Zwolle afgerond?</t>
+          <t>Hoeveel kilometer lang is de Hanzelijn tussen Lelystad en Zwolle?</t>
         </is>
       </c>
       <c r="C999" t="n">
@@ -20485,11 +20485,11 @@
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer fietspad telt Nederland bij benadering in duizenden kilometers?</t>
+          <t>Hoeveel duizend kilometer fietspad telt Nederland?</t>
         </is>
       </c>
       <c r="C1000" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D1000" t="inlineStr"/>
       <c r="E1000" t="inlineStr">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>Hoeveel miljoen koeien telt Nederland bij benadering?</t>
+          <t>Hoeveel miljoen koeien telt Nederland?</t>
         </is>
       </c>
       <c r="C1010" t="n">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>Hoeveel musea telt Amsterdam bij benadering (in tientallen)?</t>
+          <t>Hoeveel musea telt Amsterdam ongeveer?</t>
         </is>
       </c>
       <c r="C1011" t="n">
@@ -20842,11 +20842,11 @@
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>Hoeveel miljard euro is het jaarlijkse Nederlandse defensiebudget 2024 afgerond op tientallen miljarden?</t>
+          <t>Hoeveel miljard euro bedraagt het Nederlandse defensiebudget?</t>
         </is>
       </c>
       <c r="C1017" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1017" t="inlineStr"/>
       <c r="E1017" t="inlineStr">
@@ -21031,11 +21031,11 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>Hoeveel km² beslaat de provincie Utrecht ongeveer afgerond op honderdtallen?</t>
+          <t>Hoeveel vierkante kilometer groot is de provincie Utrecht?</t>
         </is>
       </c>
       <c r="C1026" t="n">
-        <v>1500</v>
+        <v>1449</v>
       </c>
       <c r="D1026" t="inlineStr"/>
       <c r="E1026" t="inlineStr">
@@ -21052,11 +21052,11 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>Hoeveel meter lang is het grootste Nederlands cruiseschip de Rotterdam (in honderden meters)?</t>
+          <t>Hoeveel meter lang is het cruiseschip Rotterdam?</t>
         </is>
       </c>
       <c r="C1027" t="n">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="D1027" t="inlineStr"/>
       <c r="E1027" t="inlineStr">
@@ -21136,11 +21136,11 @@
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>Hoeveel molens staan er op de Zaanse Schans bij benadering (in tientallen)?</t>
+          <t>Hoeveel molens staan er op de Zaanse Schans?</t>
         </is>
       </c>
       <c r="C1031" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1031" t="inlineStr"/>
       <c r="E1031" t="inlineStr">
@@ -21220,11 +21220,11 @@
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>Hoeveel duizend inwoners heeft Rotterdam bij benadering?</t>
+          <t>Hoeveel duizend inwoners heeft Rotterdam?</t>
         </is>
       </c>
       <c r="C1035" t="n">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="D1035" t="inlineStr"/>
       <c r="E1035" t="inlineStr">
@@ -21304,11 +21304,11 @@
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>Hoeveel graden Celsius is de gemiddelde zomertemperatuur in Nederland afgerond op tientallen?</t>
+          <t>Hoeveel graden Celsius is de gemiddelde zomertemperatuur in Nederland?</t>
         </is>
       </c>
       <c r="C1039" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D1039" t="inlineStr"/>
       <c r="E1039" t="inlineStr">
@@ -21325,11 +21325,11 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is het gebouw De Zalmhaven in Rotterdam afgerond op tientallen?</t>
+          <t>Hoeveel meter hoog is De Zalmhaven in Rotterdam?</t>
         </is>
       </c>
       <c r="C1040" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="D1040" t="inlineStr"/>
       <c r="E1040" t="inlineStr">
@@ -21493,7 +21493,7 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>Hoeveel liter melk drinkt de gemiddelde Nederlander per jaar afgerond op tientallen liters?</t>
+          <t>Hoeveel liter melk drinkt een Nederlander per jaar?</t>
         </is>
       </c>
       <c r="C1048" t="n">
@@ -21514,7 +21514,7 @@
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>Hoeveel bladzijden telt de Dictionary of the Dutch Language (Woordenboek der Nederlandsche Taal) in duizenden bladzijden?</t>
+          <t>Hoeveel duizend bladzijden telt het Woordenboek der Nederlandsche Taal?</t>
         </is>
       </c>
       <c r="C1049" t="n">
@@ -21577,7 +21577,7 @@
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>Hoeveel NL-doelpunten maakte Robin van Persie voor Oranje in zijn carrière afgerond op tientallen?</t>
+          <t>Hoeveel doelpunten maakte Robin van Persie voor het Nederlands elftal?</t>
         </is>
       </c>
       <c r="C1052" t="n">
@@ -21619,11 +21619,11 @@
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>Hoeveel vlindersoorten komen voor in Nederland bij benadering (in tientallen)?</t>
+          <t>Hoeveel dagvlindersoorten komen voor in Nederland?</t>
         </is>
       </c>
       <c r="C1054" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D1054" t="inlineStr"/>
       <c r="E1054" t="inlineStr">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>Hoeveel procent van de Nederlanders zegt dagelijks te fietsen (afgerond op tientallen)?</t>
+          <t>Hoeveel procent van de Nederlanders fietst dagelijks?</t>
         </is>
       </c>
       <c r="C1057" t="n">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>Hoeveel schaatsbanen van 400 meter heeft Nederland bij benadering (in tientallen)?</t>
+          <t>Hoeveel schaatsbanen van 400 meter telt Nederland?</t>
         </is>
       </c>
       <c r="C1059" t="n">
@@ -21745,7 +21745,7 @@
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Maas in Nederland bij benadering (afgerond op tientallen)?</t>
+          <t>Hoeveel kilometer van de Maas ligt in Nederland?</t>
         </is>
       </c>
       <c r="C1060" t="n">
@@ -21808,11 +21808,11 @@
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Metro van Rotterdam netwerk in totaal (afgerond op tientallen)?</t>
+          <t>Hoeveel kilometer lang is het metronet van Rotterdam?</t>
         </is>
       </c>
       <c r="C1063" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D1063" t="inlineStr"/>
       <c r="E1063" t="inlineStr">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>Hoeveel procent van de Nederlandse bevolking woont in de Randstad ongeveer (afgerond op tientallen)?</t>
+          <t>Hoeveel procent van de Nederlanders woont in de Randstad?</t>
         </is>
       </c>
       <c r="C1066" t="n">
@@ -21997,11 +21997,11 @@
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Elfstedentocht totaal afgerond op tientallen?</t>
+          <t>Hoeveel kilometer lang is de Elfstedentocht?</t>
         </is>
       </c>
       <c r="C1072" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D1072" t="inlineStr"/>
       <c r="E1072" t="inlineStr">
@@ -22039,11 +22039,11 @@
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>Hoeveel Nederlandse Nobelprijswinnaars zijn er bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel Nederlandse Nobelprijswinnaars zijn er?</t>
         </is>
       </c>
       <c r="C1074" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1074" t="inlineStr"/>
       <c r="E1074" t="inlineStr">
@@ -22060,7 +22060,7 @@
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>Hoeveel procent van de Nederlanders woont in een rijtjeshuis ongeveer (afgerond op tientallen)?</t>
+          <t>Hoeveel procent van de Nederlanders woont in een rijtjeshuis?</t>
         </is>
       </c>
       <c r="C1075" t="n">
@@ -22522,11 +22522,11 @@
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer telt de Route 66 bij benadering (in duizenden kilometers afgerond)?</t>
+          <t>Hoeveel kilometer lang was Route 66?</t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>4</v>
+        <v>3945</v>
       </c>
       <c r="D1097" t="inlineStr"/>
       <c r="E1097" t="inlineStr">
@@ -22585,11 +22585,11 @@
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>Hoeveel meter diep is de Grand Canyon op het diepste punt afgerond op honderdtallen?</t>
+          <t>Hoeveel meter diep is de Grand Canyon op het diepste punt?</t>
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>1800</v>
+        <v>1857</v>
       </c>
       <c r="D1100" t="inlineStr"/>
       <c r="E1100" t="inlineStr">
@@ -22627,11 +22627,11 @@
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>Hoeveel nationale parken telt de VS bij benadering (in tientallen)?</t>
+          <t>Hoeveel nationale parken telt de Verenigde Staten?</t>
         </is>
       </c>
       <c r="C1102" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D1102" t="inlineStr"/>
       <c r="E1102" t="inlineStr">
@@ -22732,11 +22732,11 @@
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>Hoeveel dagen duurde de Apollo 11 missie naar de maan en terug afgerond op tientallen?</t>
+          <t>Hoeveel dagen duurde de Apollo 11-missie?</t>
         </is>
       </c>
       <c r="C1107" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1107" t="inlineStr"/>
       <c r="E1107" t="inlineStr">
@@ -22921,7 +22921,7 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>Hoeveel gram suiker zit er in een blikje Coca-Cola van 12 ounce (355 ml) afgerond op tientallen?</t>
+          <t>Hoeveel gram suiker zit er in een Amerikaans blikje Coca-Cola van 355 ml?</t>
         </is>
       </c>
       <c r="C1116" t="n">
@@ -23131,7 +23131,7 @@
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>Hoeveel kg weegt een volwassen Amerikaanse bizon mannetje afgerond op honderdtallen?</t>
+          <t>Hoeveel kilogram weegt een volwassen mannelijke Amerikaanse bizon?</t>
         </is>
       </c>
       <c r="C1126" t="n">
@@ -23152,7 +23152,7 @@
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>Hoeveel soorten kolibries komen voor in de VS bij benadering (in tientallen)?</t>
+          <t>Hoeveel kolibriesoorten komen voor in de Verenigde Staten?</t>
         </is>
       </c>
       <c r="C1127" t="n">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>Hoeveel landen liggen er in Europa bij benadering (in tientallen)?</t>
+          <t>Hoeveel landen telt Europa?</t>
         </is>
       </c>
       <c r="C1136" t="n">
@@ -23446,11 +23446,11 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Rijn rivier bij benadering (in honderden km afgerond)?</t>
+          <t>Hoeveel kilometer lang is de Rijn?</t>
         </is>
       </c>
       <c r="C1141" t="n">
-        <v>1300</v>
+        <v>1230</v>
       </c>
       <c r="D1141" t="inlineStr"/>
       <c r="E1141" t="inlineStr">
@@ -23467,11 +23467,11 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Donau rivier bij benadering (in duizenden km afgerond)?</t>
+          <t>Hoeveel kilometer lang is de Donau?</t>
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>3</v>
+        <v>2850</v>
       </c>
       <c r="D1142" t="inlineStr"/>
       <c r="E1142" t="inlineStr">
@@ -23782,11 +23782,11 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is Big Ben (Elizabeth Tower) afgerond op tientallen?</t>
+          <t>Hoeveel meter hoog is de Elizabeth Tower, de toren van Big Ben?</t>
         </is>
       </c>
       <c r="C1157" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D1157" t="inlineStr"/>
       <c r="E1157" t="inlineStr">
@@ -23803,11 +23803,11 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is het Eurotunnel tussen Engeland en Frankrijk onder de zee (in tientallen km)?</t>
+          <t>Hoeveel kilometer van de Kanaaltunnel ligt onder zee?</t>
         </is>
       </c>
       <c r="C1158" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D1158" t="inlineStr"/>
       <c r="E1158" t="inlineStr">
@@ -23824,11 +23824,11 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is het Neuschwanstein Kasteel van buiten afgerond op tientallen?</t>
+          <t>Hoeveel meter hoog is kasteel Neuschwanstein?</t>
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D1159" t="inlineStr"/>
       <c r="E1159" t="inlineStr">
@@ -24055,7 +24055,7 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>Hoeveel soorten kaas produceert Frankrijk officieel bij benadering (in honderdtallen)?</t>
+          <t>Hoeveel kaassoorten produceert Frankrijk ongeveer?</t>
         </is>
       </c>
       <c r="C1170" t="n">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Hoeveel liter olijfolie gebruikt de gemiddelde Griek per jaar afgerond op tientallen?</t>
+          <t>Hoeveel liter olijfolie gebruikt een Griek per jaar?</t>
         </is>
       </c>
       <c r="C1172" t="n">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>Hoeveel soorten Duitse worsten kent de Duitse keuken bij benadering (in honderdtallen)?</t>
+          <t>Hoeveel soorten worst kent de Duitse keuken ongeveer?</t>
         </is>
       </c>
       <c r="C1173" t="n">
@@ -24181,11 +24181,11 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>Hoeveel piano sonates schreef Beethoven bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel pianosonates schreef Beethoven?</t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D1176" t="inlineStr"/>
       <c r="E1176" t="inlineStr">
@@ -24202,11 +24202,11 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Hoeveel symfonieën schreef Mozart bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel symfonieën schreef Mozart?</t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D1177" t="inlineStr"/>
       <c r="E1177" t="inlineStr">
@@ -24265,11 +24265,11 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>Hoeveel toneelstukken schreef Shakespeare bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel toneelstukken schreef Shakespeare volgens de gangbare telling?</t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1180" t="inlineStr"/>
       <c r="E1180" t="inlineStr">
@@ -24433,11 +24433,11 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Hoeveel leden telt de Raad van Europa (2024) bij benadering (in tientallen)?</t>
+          <t>Hoeveel landen zijn lid van de Raad van Europa?</t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D1188" t="inlineStr"/>
       <c r="E1188" t="inlineStr">
@@ -24496,11 +24496,11 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Hoeveel landen telt Azië bij benadering (in tientallen)?</t>
+          <t>Hoeveel landen telt Azië?</t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D1191" t="inlineStr"/>
       <c r="E1191" t="inlineStr">
@@ -24601,11 +24601,11 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Hoeveel officiële talen erkent India landelijk bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel talen erkent India als officiële taal?</t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1196" t="inlineStr"/>
       <c r="E1196" t="inlineStr">
@@ -24685,11 +24685,11 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Hoeveel provincies heeft China bij benadering (in tientallen)?</t>
+          <t>Hoeveel provincies telt China?</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D1200" t="inlineStr"/>
       <c r="E1200" t="inlineStr">
@@ -24727,11 +24727,11 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Ganges rivier bij benadering (in duizenden km afgerond)?</t>
+          <t>Hoeveel kilometer lang is de Ganges?</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>3</v>
+        <v>2525</v>
       </c>
       <c r="D1202" t="inlineStr"/>
       <c r="E1202" t="inlineStr">
@@ -24769,11 +24769,11 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is K2 afgerond op honderdtallen?</t>
+          <t>Hoeveel meter hoog is de K2?</t>
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>8600</v>
+        <v>8611</v>
       </c>
       <c r="D1204" t="inlineStr"/>
       <c r="E1204" t="inlineStr">
@@ -24811,11 +24811,11 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Grote Muur van China officieel gemeten (2024 in duizenden km afgerond)?</t>
+          <t>Hoeveel kilometer lang is de Grote Muur van China volgens de officiële meting?</t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>21</v>
+        <v>21196</v>
       </c>
       <c r="D1206" t="inlineStr"/>
       <c r="E1206" t="inlineStr">
@@ -24853,11 +24853,11 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is de Shanghai Tower afgerond op honderdtallen?</t>
+          <t>Hoeveel meter hoog is de Shanghai Tower?</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>600</v>
+        <v>632</v>
       </c>
       <c r="D1208" t="inlineStr"/>
       <c r="E1208" t="inlineStr">
@@ -24895,11 +24895,11 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is de Taj Mahal afgerond op tientallen?</t>
+          <t>Hoeveel meter hoog is de Taj Mahal?</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D1210" t="inlineStr"/>
       <c r="E1210" t="inlineStr">
@@ -24958,11 +24958,11 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is de Tokyo Tower afgerond op tientallen?</t>
+          <t>Hoeveel meter hoog is de Tokyo Tower?</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D1213" t="inlineStr"/>
       <c r="E1213" t="inlineStr">
@@ -25084,11 +25084,11 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Hoeveel dynastieën telt de Chinese geschiedenis bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel dynastieën telt de Chinese geschiedenis ongeveer?</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D1219" t="inlineStr"/>
       <c r="E1219" t="inlineStr">
@@ -25168,11 +25168,11 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Hoeveel procent van de wereldbevolking is boeddhistisch bij benadering (in tientallen procenten)?</t>
+          <t>Hoeveel procent van de wereldbevolking is boeddhistisch?</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D1223" t="inlineStr"/>
       <c r="E1223" t="inlineStr">
@@ -25273,7 +25273,7 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Hoeveel dagen duurt de Ramadan per jaar (maanmaand afgerond op tientallen)?</t>
+          <t>Hoeveel dagen duurt de Ramadan maximaal?</t>
         </is>
       </c>
       <c r="C1228" t="n">
@@ -25294,7 +25294,7 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Hoeveel pelgrims bezoeken Mekka jaarlijks bij benadering (in miljoenen)?</t>
+          <t>Hoeveel miljoen pelgrims bezoeken Mekka jaarlijks?</t>
         </is>
       </c>
       <c r="C1229" t="n">
@@ -25441,7 +25441,7 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Hoeveel snaren heeft de Indiase sitar bij benadering (in tientallen)?</t>
+          <t>Hoeveel snaren heeft een Indiase sitar?</t>
         </is>
       </c>
       <c r="C1236" t="n">
@@ -25462,11 +25462,11 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Hoeveel snaren heeft de klassieke Chinese guzheng bij benadering (in tientallen)?</t>
+          <t>Hoeveel snaren heeft een Chinese guzheng?</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1237" t="inlineStr"/>
       <c r="E1237" t="inlineStr">
@@ -25504,7 +25504,7 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Hoeveel kilogram weegt een volwassen Aziatische olifant afgerond op duizendtallen?</t>
+          <t>Hoeveel kilogram weegt een volwassen Aziatische olifant?</t>
         </is>
       </c>
       <c r="C1239" t="n">
@@ -25525,11 +25525,11 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Hoeveel kilogram weegt een volwassen Bengaalse tijger afgerond op honderdtallen?</t>
+          <t>Hoeveel kilogram weegt een volwassen mannelijke Bengaalse tijger?</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="D1240" t="inlineStr"/>
       <c r="E1240" t="inlineStr">
@@ -25735,11 +25735,11 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer per uur rijdt de Shanghai Maglev trein (afgerond op tientallen)?</t>
+          <t>Hoeveel kilometer per uur haalt de Shanghai Maglev?</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D1250" t="inlineStr"/>
       <c r="E1250" t="inlineStr">
@@ -25840,11 +25840,11 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>Hoeveel Chinezen wonen er in China bij benadering (in miljarden afgerond op halve)?</t>
+          <t>Hoeveel miljoen inwoners heeft China?</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>1</v>
+        <v>1410</v>
       </c>
       <c r="D1255" t="inlineStr"/>
       <c r="E1255" t="inlineStr">
@@ -25861,11 +25861,11 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Hoeveel Indiërs wonen er in India bij benadering (in miljarden)?</t>
+          <t>Hoeveel miljoen inwoners heeft India?</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>1</v>
+        <v>1440</v>
       </c>
       <c r="D1256" t="inlineStr"/>
       <c r="E1256" t="inlineStr">
@@ -25924,11 +25924,11 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>Hoeveel Afrikaanse landen grenzen aan de Atlantische Oceaan bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel Afrikaanse landen grenzen aan de Atlantische Oceaan?</t>
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D1259" t="inlineStr"/>
       <c r="E1259" t="inlineStr">
@@ -25966,11 +25966,11 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>Hoeveel landen heeft de Nijl als bron of doorstroom bij benadering (in tientallen afgerond)?</t>
+          <t>Door hoeveel landen stroomt de Nijl of een van zijn zijrivieren?</t>
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D1261" t="inlineStr"/>
       <c r="E1261" t="inlineStr">
@@ -26008,7 +26008,7 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>Hoeveel landen heeft de Sahara deels in zijn gebied bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel landen hebben grondgebied in de Sahara?</t>
         </is>
       </c>
       <c r="C1263" t="n">
@@ -26029,11 +26029,11 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is de Kilimanjaro (Uhuru Peak) afgerond op honderdtallen?</t>
+          <t>Hoeveel meter hoog is de Kilimanjaro?</t>
         </is>
       </c>
       <c r="C1264" t="n">
-        <v>5900</v>
+        <v>5895</v>
       </c>
       <c r="D1264" t="inlineStr"/>
       <c r="E1264" t="inlineStr">
@@ -26050,7 +26050,7 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Kalahari woestijn bij benadering (in honderden km afgerond)?</t>
+          <t>Hoeveel kilometer breed is de Kalahariwoestijn ongeveer?</t>
         </is>
       </c>
       <c r="C1265" t="n">
@@ -26071,7 +26071,7 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>Hoeveel landen telt de Sahel-regio bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel landen telt de Sahel-regio?</t>
         </is>
       </c>
       <c r="C1266" t="n">
@@ -26113,11 +26113,11 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is de Grote Piramide van Gizeh afgerond op tientallen?</t>
+          <t>Hoeveel meter hoog is de Grote Piramide van Gizeh nu?</t>
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D1268" t="inlineStr"/>
       <c r="E1268" t="inlineStr">
@@ -26134,11 +26134,11 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is de Toren van Caïro (Cairo Tower) afgerond op tientallen?</t>
+          <t>Hoeveel meter hoog is de Cairo Tower?</t>
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D1269" t="inlineStr"/>
       <c r="E1269" t="inlineStr">
@@ -26176,7 +26176,7 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>Hoeveel bekende piramides telt Egypte in totaal bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel piramides telt Egypte ongeveer?</t>
         </is>
       </c>
       <c r="C1271" t="n">
@@ -26197,11 +26197,11 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Suezkanaal (in tientallen km afgerond)?</t>
+          <t>Hoeveel kilometer lang is het Suezkanaal?</t>
         </is>
       </c>
       <c r="C1272" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D1272" t="inlineStr"/>
       <c r="E1272" t="inlineStr">
@@ -26365,11 +26365,11 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>Hoeveel jaar regeerde Cleopatra VII bij benadering (in tientallen jaar afgerond)?</t>
+          <t>Hoeveel jaar regeerde Cleopatra VII?</t>
         </is>
       </c>
       <c r="C1280" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1280" t="inlineStr"/>
       <c r="E1280" t="inlineStr">
@@ -26407,7 +26407,7 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer per uur kan een cheetah sprinten (afgerond op tientallen)?</t>
+          <t>Hoeveel kilometer per uur haalt een cheetah op zijn snelst?</t>
         </is>
       </c>
       <c r="C1282" t="n">
@@ -26428,7 +26428,7 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>Hoeveel kilogram weegt een volwassen Afrikaanse olifant mannetje afgerond op duizendtallen?</t>
+          <t>Hoeveel kilogram weegt een volwassen mannetjesolifant in Afrika?</t>
         </is>
       </c>
       <c r="C1283" t="n">
@@ -26449,7 +26449,7 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>Hoeveel kilogram weegt een volwassen Nijlpaard afgerond op honderdtallen?</t>
+          <t>Hoeveel kilogram weegt een volwassen nijlpaard?</t>
         </is>
       </c>
       <c r="C1284" t="n">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Hoeveel meter lang kan een volwassen Nijlkrokodil worden afgerond op halve meters?</t>
+          <t>Hoeveel meter lang kan een volwassen nijlkrokodil worden?</t>
         </is>
       </c>
       <c r="C1285" t="n">
@@ -26491,11 +26491,11 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Hoeveel procent van de leeuwenpopulatie leeft in Sub-Sahara Afrika (afgerond op tientallen)?</t>
+          <t>Hoeveel procent van de wilde leeuwen leeft in Sub-Sahara Afrika?</t>
         </is>
       </c>
       <c r="C1286" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D1286" t="inlineStr"/>
       <c r="E1286" t="inlineStr">
@@ -26533,11 +26533,11 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is de Victoriawatervallen afgerond op tientallen?</t>
+          <t>Hoeveel meter hoog zijn de Victoriawatervallen?</t>
         </is>
       </c>
       <c r="C1288" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D1288" t="inlineStr"/>
       <c r="E1288" t="inlineStr">
@@ -26554,11 +26554,11 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Hoeveel meter breed is de Victoriawatervallen bij benadering (in honderden meters afgerond)?</t>
+          <t>Hoeveel meter breed zijn de Victoriawatervallen?</t>
         </is>
       </c>
       <c r="C1289" t="n">
-        <v>1700</v>
+        <v>1708</v>
       </c>
       <c r="D1289" t="inlineStr"/>
       <c r="E1289" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Hoeveel landen produceren koffie in Afrika bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel Afrikaanse landen produceren koffie?</t>
         </is>
       </c>
       <c r="C1291" t="n">
@@ -26722,11 +26722,11 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Hoeveel landen gebruiken de West-Afrikaanse CFA frank bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel landen gebruiken de West-Afrikaanse CFA-frank?</t>
         </is>
       </c>
       <c r="C1297" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1297" t="inlineStr"/>
       <c r="E1297" t="inlineStr">
@@ -26785,11 +26785,11 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>Hoeveel provincies heeft Nieuw-Zeeland bij benadering (in tientallen afgerond - regions)?</t>
+          <t>Hoeveel regio's telt Nieuw-Zeeland?</t>
         </is>
       </c>
       <c r="C1300" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D1300" t="inlineStr"/>
       <c r="E1300" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>Hoeveel eilanden telt het Great Barrier Reef bij benadering (in honderden afgerond)?</t>
+          <t>Hoeveel eilanden telt het Great Barrier Reef?</t>
         </is>
       </c>
       <c r="C1303" t="n">
@@ -26869,11 +26869,11 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>Hoeveel eilanden heeft Fiji bij benadering (in honderden afgerond)?</t>
+          <t>Hoeveel eilanden telt Fiji?</t>
         </is>
       </c>
       <c r="C1304" t="n">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="D1304" t="inlineStr"/>
       <c r="E1304" t="inlineStr">
@@ -26890,7 +26890,7 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>Hoeveel eilanden heeft Papoea-Nieuw-Guinea bij benadering (in honderden afgerond)?</t>
+          <t>Hoeveel eilanden telt Papoea-Nieuw-Guinea ongeveer?</t>
         </is>
       </c>
       <c r="C1305" t="n">
@@ -26911,11 +26911,11 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is Mount Cook (Aoraki) afgerond op honderdtallen?</t>
+          <t>Hoeveel meter hoog is Mount Cook (Aoraki)?</t>
         </is>
       </c>
       <c r="C1306" t="n">
-        <v>3700</v>
+        <v>3724</v>
       </c>
       <c r="D1306" t="inlineStr"/>
       <c r="E1306" t="inlineStr">
@@ -26932,11 +26932,11 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is Uluru (Ayers Rock) afgerond op tientallen?</t>
+          <t>Hoeveel meter hoog is Uluru?</t>
         </is>
       </c>
       <c r="C1307" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D1307" t="inlineStr"/>
       <c r="E1307" t="inlineStr">
@@ -26953,7 +26953,7 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>Hoeveel nationale parken telt Australië bij benadering (in honderden afgerond)?</t>
+          <t>Hoeveel nationale parken telt Australië ongeveer?</t>
         </is>
       </c>
       <c r="C1308" t="n">
@@ -26974,11 +26974,11 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Australische kustlijn bij benadering (in duizenden km afgerond)?</t>
+          <t>Hoeveel duizend kilometer lang is de Australische kustlijn?</t>
         </is>
       </c>
       <c r="C1309" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D1309" t="inlineStr"/>
       <c r="E1309" t="inlineStr">
@@ -27100,7 +27100,7 @@
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>Hoeveel kg weegt een volwassen mannelijke kangoeroe afgerond op tientallen?</t>
+          <t>Hoeveel kilogram weegt een volwassen mannelijke rode reuzenkangoeroe maximaal?</t>
         </is>
       </c>
       <c r="C1315" t="n">
@@ -27121,7 +27121,7 @@
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>Hoeveel uur per dag slaapt een koala bij benadering (in tientallen uur afgerond)?</t>
+          <t>Hoeveel uur per dag slaapt een koala?</t>
         </is>
       </c>
       <c r="C1316" t="n">
@@ -27142,11 +27142,11 @@
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>Hoeveel soorten kangoeroes bevat de macropod-familie bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel soorten telt de kangoeroefamilie (Macropodidae)?</t>
         </is>
       </c>
       <c r="C1317" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D1317" t="inlineStr"/>
       <c r="E1317" t="inlineStr">
@@ -27163,11 +27163,11 @@
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Hoeveel cm lang wordt een volwassen emoe vrouwtje bij benadering (in tientallen cm)?</t>
+          <t>Hoeveel centimeter hoog wordt een volwassen emoe?</t>
         </is>
       </c>
       <c r="C1318" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="D1318" t="inlineStr"/>
       <c r="E1318" t="inlineStr">
@@ -27331,11 +27331,11 @@
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>Hoeveel Grammy won de Australische band AC/DC bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel Grammy's won AC/DC?</t>
         </is>
       </c>
       <c r="C1326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1326" t="inlineStr"/>
       <c r="E1326" t="inlineStr">
@@ -27373,11 +27373,11 @@
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>Hoeveel albums bracht de Australische band Midnight Oil uit bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel studioalbums bracht Midnight Oil uit?</t>
         </is>
       </c>
       <c r="C1328" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D1328" t="inlineStr"/>
       <c r="E1328" t="inlineStr">
@@ -27436,11 +27436,11 @@
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>Hoeveel uur duurt de film Avatar: The Way of Water bij benadering (in hele uren afgerond)?</t>
+          <t>Hoeveel minuten duurt de film Avatar: The Way of Water?</t>
         </is>
       </c>
       <c r="C1331" t="n">
-        <v>3</v>
+        <v>192</v>
       </c>
       <c r="D1331" t="inlineStr"/>
       <c r="E1331" t="inlineStr">
@@ -27457,11 +27457,11 @@
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>Hoeveel zetels telt het Australische Huis van Afgevaardigden (House of Representatives) bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel zetels telt het Australische Huis van Afgevaardigden?</t>
         </is>
       </c>
       <c r="C1332" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D1332" t="inlineStr"/>
       <c r="E1332" t="inlineStr">
@@ -27499,11 +27499,11 @@
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>Hoeveel landen telt Oceanië bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel landen telt Oceanië?</t>
         </is>
       </c>
       <c r="C1334" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D1334" t="inlineStr"/>
       <c r="E1334" t="inlineStr">
@@ -27520,11 +27520,11 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Hoeveel landen telt het Pacific Islands Forum bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel landen zijn lid van het Pacific Islands Forum?</t>
         </is>
       </c>
       <c r="C1335" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D1335" t="inlineStr"/>
       <c r="E1335" t="inlineStr">
@@ -27541,11 +27541,11 @@
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>Hoeveel landen telt Midden-Amerika (inclusief Mexico bij sommige tellingen) bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel landen telt Midden-Amerika?</t>
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D1336" t="inlineStr"/>
       <c r="E1336" t="inlineStr">
@@ -27667,7 +27667,7 @@
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>Hoeveel vierkante kilometer beslaat het Amazone regenwoud bij benadering (in miljoenen km² afgerond)?</t>
+          <t>Hoeveel miljoen vierkante kilometer beslaat het Amazoneregenwoud?</t>
         </is>
       </c>
       <c r="C1342" t="n">
@@ -27709,11 +27709,11 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>Hoeveel landen deelt de Andes bergketen bij benadering (in tientallen afgerond)?</t>
+          <t>Door hoeveel landen loopt het Andesgebergte?</t>
         </is>
       </c>
       <c r="C1344" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D1344" t="inlineStr"/>
       <c r="E1344" t="inlineStr">
@@ -27730,11 +27730,11 @@
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is de Aconcagua (hoogste piek van de Andes en buiten-Azië) afgerond op honderdtallen?</t>
+          <t>Hoeveel meter hoog is de Aconcagua?</t>
         </is>
       </c>
       <c r="C1345" t="n">
-        <v>7000</v>
+        <v>6961</v>
       </c>
       <c r="D1345" t="inlineStr"/>
       <c r="E1345" t="inlineStr">
@@ -27814,11 +27814,11 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Hoeveel sluizen heeft het Panamakanaal bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel sluizen heeft het Panamakanaal?</t>
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D1349" t="inlineStr"/>
       <c r="E1349" t="inlineStr">
@@ -27835,11 +27835,11 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Metro van Mexico-Stad netwerk bij benadering (in honderden km afgerond)?</t>
+          <t>Hoeveel kilometer lang is het metronet van Mexico-Stad?</t>
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D1350" t="inlineStr"/>
       <c r="E1350" t="inlineStr">
@@ -27877,11 +27877,11 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>Hoeveel verdiepingen heeft het woontoren BD Bacatá in Bogotá bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel verdiepingen heeft de BD Bacatá in Bogotá?</t>
         </is>
       </c>
       <c r="C1352" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D1352" t="inlineStr"/>
       <c r="E1352" t="inlineStr">
@@ -28045,7 +28045,7 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>Hoeveel soorten vogels telt de Amazone bij benadering (in honderden afgerond)?</t>
+          <t>Hoeveel vogelsoorten telt het Amazonegebied?</t>
         </is>
       </c>
       <c r="C1360" t="n">
@@ -28087,7 +28087,7 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>Hoeveel kilogram weegt een volwassen jaguar mannetje afgerond op tientallen?</t>
+          <t>Hoeveel kilogram weegt een volwassen mannelijke jaguar?</t>
         </is>
       </c>
       <c r="C1362" t="n">
@@ -28108,7 +28108,7 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>Hoeveel meter lang kan een groene anaconda worden afgerond op hele meters?</t>
+          <t>Hoeveel meter lang kan een groene anaconda worden?</t>
         </is>
       </c>
       <c r="C1363" t="n">
@@ -28129,7 +28129,7 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>Hoeveel soorten apen telt het Amazonegebied bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel apensoorten telt het Amazonegebied ongeveer?</t>
         </is>
       </c>
       <c r="C1364" t="n">
@@ -28150,7 +28150,7 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Hoeveel kilogram koffie produceert Brazilië jaarlijks bij benadering (in miljoenen zakken afgerond op tientallen)?</t>
+          <t>Hoeveel miljoen zakken koffie produceert Brazilië per jaar?</t>
         </is>
       </c>
       <c r="C1365" t="n">
@@ -28171,11 +28171,11 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Hoeveel procent van de wereldkoffie wordt geproduceerd door Brazilië (afgerond op tientallen)?</t>
+          <t>Hoeveel procent van de wereldkoffie komt uit Brazilië?</t>
         </is>
       </c>
       <c r="C1366" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D1366" t="inlineStr"/>
       <c r="E1366" t="inlineStr">
@@ -28213,7 +28213,7 @@
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>Hoeveel kilogram rundvlees eet de gemiddelde Argentijn per jaar bij benadering (in tientallen kg afgerond)?</t>
+          <t>Hoeveel kilogram rundvlees eet een Argentijn per jaar?</t>
         </is>
       </c>
       <c r="C1368" t="n">
@@ -28255,7 +28255,7 @@
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>Hoeveel muzikanten heeft een klassieke mariachi band bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel muzikanten telt een klassieke mariachiband?</t>
         </is>
       </c>
       <c r="C1370" t="n">
@@ -28486,11 +28486,11 @@
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Hoeveel landen telt de CELAC organisatie bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel landen zijn lid van de CELAC?</t>
         </is>
       </c>
       <c r="C1381" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="inlineStr">
@@ -28906,11 +28906,11 @@
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Kongorivier bij benadering (in duizenden km afgerond)?</t>
+          <t>Hoeveel kilometer lang is de Kongo?</t>
         </is>
       </c>
       <c r="C1401" t="n">
-        <v>5</v>
+        <v>4700</v>
       </c>
       <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="inlineStr">
@@ -28927,11 +28927,11 @@
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Nigerrivier bij benadering (in duizenden km afgerond)?</t>
+          <t>Hoeveel kilometer lang is de Niger?</t>
         </is>
       </c>
       <c r="C1402" t="n">
-        <v>4</v>
+        <v>4200</v>
       </c>
       <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="inlineStr">
@@ -28948,11 +28948,11 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Zambezirivier bij benadering (in duizenden km afgerond)?</t>
+          <t>Hoeveel kilometer lang is de Zambezi?</t>
         </is>
       </c>
       <c r="C1403" t="n">
-        <v>3</v>
+        <v>2574</v>
       </c>
       <c r="D1403" t="inlineStr"/>
       <c r="E1403" t="inlineStr">
@@ -28969,11 +28969,11 @@
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is Mount Kenya afgerond op honderdtallen?</t>
+          <t>Hoeveel meter hoog is Mount Kenya?</t>
         </is>
       </c>
       <c r="C1404" t="n">
-        <v>5200</v>
+        <v>5199</v>
       </c>
       <c r="D1404" t="inlineStr"/>
       <c r="E1404" t="inlineStr">
@@ -28990,11 +28990,11 @@
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is de Toubkal, hoogste piek van het Atlasgebergte, afgerond op honderdtallen?</t>
+          <t>Hoeveel meter hoog is de Toubkal, de hoogste top van het Atlasgebergte?</t>
         </is>
       </c>
       <c r="C1405" t="n">
-        <v>4200</v>
+        <v>4167</v>
       </c>
       <c r="D1405" t="inlineStr"/>
       <c r="E1405" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>Hoeveel keer meer pyramides telt Soedan dan Egypte bij benadering?</t>
+          <t>Hoeveel keer meer piramides heeft Soedan dan Egypte?</t>
         </is>
       </c>
       <c r="C1411" t="n">
@@ -29137,7 +29137,7 @@
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer per uur sprint een leeuw afgerond op tientallen?</t>
+          <t>Hoeveel kilometer per uur sprint een leeuw?</t>
         </is>
       </c>
       <c r="C1412" t="n">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>Hoeveel kilogram weegt een volwassen witte neushoorn afgerond op duizendtallen?</t>
+          <t>Hoeveel kilogram weegt een volwassen witte neushoorn?</t>
         </is>
       </c>
       <c r="C1413" t="n">
@@ -29179,7 +29179,7 @@
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>Hoeveel kilogram weegt een volwassen giraffe afgerond op honderdtallen?</t>
+          <t>Hoeveel kilogram weegt een volwassen giraffe?</t>
         </is>
       </c>
       <c r="C1414" t="n">
@@ -29200,7 +29200,7 @@
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>Hoeveel meter lang wordt een Afrikaanse olifant afgerond op hele meters?</t>
+          <t>Hoeveel meter lang wordt een Afrikaanse olifant?</t>
         </is>
       </c>
       <c r="C1415" t="n">
@@ -29221,7 +29221,7 @@
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>Hoeveel soorten lemuren telt Madagaskar bij benadering (in tientallen)?</t>
+          <t>Hoeveel lemuursoorten telt Madagaskar ongeveer?</t>
         </is>
       </c>
       <c r="C1416" t="n">
@@ -29242,7 +29242,7 @@
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>Hoeveel procent van de wereldcacao komt uit West-Afrika afgerond op tientallen?</t>
+          <t>Hoeveel procent van de wereldcacao komt uit West-Afrika?</t>
         </is>
       </c>
       <c r="C1417" t="n">
@@ -29263,7 +29263,7 @@
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>Hoeveel miljoen gnoes doen mee aan de Grote Migratie in de Serengeti (afgerond op miljoenen)?</t>
+          <t>Hoeveel miljoen gnoes trekken mee in de Grote Migratie van de Serengeti?</t>
         </is>
       </c>
       <c r="C1418" t="n">
@@ -29326,11 +29326,11 @@
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>Hoeveel snaren heeft de Ethiopische krar bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel snaren heeft de Ethiopische krar?</t>
         </is>
       </c>
       <c r="C1421" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1421" t="inlineStr"/>
       <c r="E1421" t="inlineStr">
@@ -29410,11 +29410,11 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is Mount Kosciuszko, het hoogste punt van Australië, afgerond op honderdtallen?</t>
+          <t>Hoeveel meter hoog is Mount Kosciuszko, het hoogste punt van Australië?</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>2200</v>
+        <v>2228</v>
       </c>
       <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="inlineStr">
@@ -29431,11 +29431,11 @@
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is de Murrayrivier bij benadering (in duizenden km afgerond)?</t>
+          <t>Hoeveel kilometer lang is de Murray?</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>3</v>
+        <v>2508</v>
       </c>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="inlineStr">
@@ -29452,7 +29452,7 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>Hoeveel procent van Australië bestaat uit woestijn of droog gebied (afgerond op tientallen)?</t>
+          <t>Hoeveel procent van Australië is woestijn of droog gebied?</t>
         </is>
       </c>
       <c r="C1427" t="n">
@@ -29473,7 +29473,7 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Hoeveel miljoen inwoners heeft Australië (2024, afgerond)?</t>
+          <t>Hoeveel miljoen inwoners heeft Australië?</t>
         </is>
       </c>
       <c r="C1428" t="n">
@@ -29494,7 +29494,7 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Hoeveel miljoen inwoners heeft Nieuw-Zeeland (2024, afgerond)?</t>
+          <t>Hoeveel miljoen inwoners heeft Nieuw-Zeeland?</t>
         </is>
       </c>
       <c r="C1429" t="n">
@@ -29536,11 +29536,11 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is de Sydney Tower afgerond op tientallen?</t>
+          <t>Hoeveel meter hoog is de Sydney Tower?</t>
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D1431" t="inlineStr"/>
       <c r="E1431" t="inlineStr">
@@ -29578,11 +29578,11 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Hoeveel soorten vogels telt Australië bij benadering (in honderden afgerond)?</t>
+          <t>Hoeveel vogelsoorten telt Australië?</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>800</v>
+        <v>830</v>
       </c>
       <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="inlineStr">
@@ -29599,11 +29599,11 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Hoeveel kilogram weegt een volwassen emoe afgerond op tientallen?</t>
+          <t>Hoeveel kilogram weegt een volwassen emoe?</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="inlineStr">
@@ -29641,7 +29641,7 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Hoeveel meter lang wordt een zoutwaterkrokodil maximaal afgerond op hele meters?</t>
+          <t>Hoeveel meter lang wordt een zoutwaterkrokodil maximaal?</t>
         </is>
       </c>
       <c r="C1436" t="n">
@@ -29662,7 +29662,7 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>Hoeveel kilogram weegt een volwassen wombat afgerond op tientallen?</t>
+          <t>Hoeveel kilogram weegt een volwassen wombat?</t>
         </is>
       </c>
       <c r="C1437" t="n">
@@ -29746,11 +29746,11 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Hoeveel studioalbums bracht Kylie Minogue uit bij benadering (in tientallen afgerond)?</t>
+          <t>Hoeveel studioalbums bracht Kylie Minogue uit?</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1441" t="inlineStr"/>
       <c r="E1441" t="inlineStr">
@@ -30103,11 +30103,11 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Hoeveel miljoen inwoners heeft Brazilië (2024, afgerond op honderdtallen)?</t>
+          <t>Hoeveel miljoen inwoners heeft Brazilië?</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D1458" t="inlineStr"/>
       <c r="E1458" t="inlineStr">
@@ -30124,11 +30124,11 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Hoeveel miljoen inwoners heeft Mexico (2024, afgerond op honderdtallen)?</t>
+          <t>Hoeveel miljoen inwoners heeft Mexico?</t>
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D1459" t="inlineStr"/>
       <c r="E1459" t="inlineStr">
@@ -30145,11 +30145,11 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>Hoeveel miljoen inwoners heeft Argentinië (2024, afgerond op tientallen)?</t>
+          <t>Hoeveel miljoen inwoners heeft Argentinië?</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="inlineStr">
@@ -30166,11 +30166,11 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>Hoeveel miljoen inwoners heeft Colombia (2024, afgerond op tientallen)?</t>
+          <t>Hoeveel miljoen inwoners heeft Colombia?</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="inlineStr">
@@ -30187,11 +30187,11 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Hoeveel miljoen inwoners heeft Peru (2024, afgerond op tientallen)?</t>
+          <t>Hoeveel miljoen inwoners heeft Peru?</t>
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D1462" t="inlineStr"/>
       <c r="E1462" t="inlineStr">
@@ -30208,7 +30208,7 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Hoeveel miljoen inwoners heeft Chili (2024, afgerond op tientallen)?</t>
+          <t>Hoeveel miljoen inwoners heeft Chili?</t>
         </is>
       </c>
       <c r="C1463" t="n">
@@ -30250,11 +30250,11 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Hoeveel meter hoog is Christus Redentor inclusief sokkel afgerond op tientallen?</t>
+          <t>Hoeveel meter hoog is het Christus Verlosser-beeld zonder sokkel?</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="inlineStr">
@@ -30481,7 +30481,7 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Hoeveel soorten vogels telt Colombia bij benadering (in honderden afgerond)?</t>
+          <t>Hoeveel vogelsoorten telt Colombia, het land met de meeste ter wereld?</t>
         </is>
       </c>
       <c r="C1476" t="n">
@@ -30502,7 +30502,7 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer per uur sprint een jaguar afgerond op tientallen?</t>
+          <t>Hoeveel kilometer per uur sprint een jaguar?</t>
         </is>
       </c>
       <c r="C1477" t="n">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Hoeveel kilometer lang is een halve marathon (afgerond)?</t>
+          <t>Hoeveel kilometer lang is een halve marathon?</t>
         </is>
       </c>
       <c r="C1493" t="n">

--- a/vragen/1000+ vragen netjes gecategoriseerd.xlsx
+++ b/vragen/1000+ vragen netjes gecategoriseerd.xlsx
@@ -9307,11 +9307,11 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>1000</v>
+        <v>1305</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://www.guinnessworldrecords.com/world-records/most-marathons-run</t>
+          <t>https://www.guinnessworldrecords.com/world-records/64777-most-marathons-completed</t>
         </is>
       </c>
     </row>
@@ -9383,15 +9383,15 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Hoeveel uur duurde het langste videogame-marathonrecord?</t>
+          <t>Hoeveel uur duurde het langste videogame-marathonrecord (stand 2026)?</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>https://www.guinnessworldrecords.com/world-records/longest-videogames-marathon</t>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-video-games-marathon</t>
         </is>
       </c>
     </row>
@@ -26366,7 +26366,7 @@
       </c>
       <c r="D1204" t="inlineStr">
         <is>
-          <t>https://www.guinnessworldrecords.com/world-records/highest-dive</t>
+          <t>https://www.guinnessworldrecords.com/world-records/407825-highest-cliff-jump</t>
         </is>
       </c>
     </row>
@@ -26642,11 +26642,11 @@
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>1000</v>
+        <v>1508</v>
       </c>
       <c r="D1218" t="inlineStr">
         <is>
-          <t>https://www.guinnessworldrecords.com/</t>
+          <t>https://www.guinnessworldrecords.com/world-records/68643-most-people-juggling-simultaneously</t>
         </is>
       </c>
     </row>

--- a/vragen/1000+ vragen netjes gecategoriseerd.xlsx
+++ b/vragen/1000+ vragen netjes gecategoriseerd.xlsx
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://nl.wikipedia.org/wiki/Mars</t>
+          <t>https://nl.wikipedia.org/wiki/Mars_(planeet)</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/HC_Klein_Zwitserland</t>
+          <t>https://nl.wikipedia.org/wiki/Zwitserland</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/UNESCO</t>
+          <t>https://ich.unesco.org/en/intangible-heritage-domains-00052</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://nl.wikipedia.org/wiki/Bad_Bunny</t>
+          <t>https://en.wikipedia.org/wiki/Un_Verano_Sin_Ti</t>
         </is>
       </c>
     </row>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>https://nl.wikipedia.org/wiki/Boeing</t>
+          <t>https://nl.wikipedia.org/wiki/Boeing_747</t>
         </is>
       </c>
     </row>
@@ -13741,7 +13741,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>https://nl.wikipedia.org/wiki/Schorpioenen_%28dieren%29</t>
+          <t>https://nl.wikipedia.org/wiki/Chinese_astrologie</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Chili</t>
+          <t>https://en.wikipedia.org/wiki/Chile</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
@@ -23731,7 +23731,7 @@
       </c>
       <c r="D1094" t="inlineStr">
         <is>
-          <t>https://nl.wikipedia.org/wiki/Utrecht_%28stad%29</t>
+          <t>https://nl.wikipedia.org/wiki/Nederlands_Film_Festival</t>
         </is>
       </c>
       <c r="E1094" t="inlineStr">
@@ -27401,7 +27401,7 @@
       </c>
       <c r="D1254" t="inlineStr">
         <is>
-          <t>https://nl.wikipedia.org/wiki/Olympische_Zomerspelen</t>
+          <t>https://nl.wikipedia.org/wiki/Olympische_Zomerspelen_2024</t>
         </is>
       </c>
       <c r="E1254" t="inlineStr">

--- a/vragen/1000+ vragen netjes gecategoriseerd.xlsx
+++ b/vragen/1000+ vragen netjes gecategoriseerd.xlsx
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>338000</v>
+        <v>338226</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>8100</v>
+        <v>8095</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>26000</v>
+        <v>26090</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>100000</v>
+        <v>100984</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>8000</v>
+        <v>8957</v>
       </c>
       <c r="D1220" t="inlineStr">
         <is>
